--- a/Grout Stats/CI-PRO-001_REG-001 ROTURA DE GROUT 006.xlsx
+++ b/Grout Stats/CI-PRO-001_REG-001 ROTURA DE GROUT 006.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Powerchina\Tecnopilotes\Registros de Calidad\06 AG-09 (30-01-26)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E575967A-8A81-4A2D-B505-72D1B3994A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FBF04FF-935C-432B-8C1A-90E492864CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -199,21 +199,6 @@
     <t>Aerogenerador #09</t>
   </si>
   <si>
-    <t>TE-0127</t>
-  </si>
-  <si>
-    <t>TE-0128</t>
-  </si>
-  <si>
-    <t>TE-0129</t>
-  </si>
-  <si>
-    <t>TE-0130</t>
-  </si>
-  <si>
-    <t>TE-0131</t>
-  </si>
-  <si>
     <t>Sikagrout 9401</t>
   </si>
   <si>
@@ -223,16 +208,31 @@
     <t>Sikagrout 9403</t>
   </si>
   <si>
-    <t>TE-0132</t>
-  </si>
-  <si>
-    <t>TE-0133</t>
-  </si>
-  <si>
-    <t>TE-0135</t>
-  </si>
-  <si>
-    <t>TE-0136</t>
+    <t>TE-127</t>
+  </si>
+  <si>
+    <t>TE-128</t>
+  </si>
+  <si>
+    <t>TE-129</t>
+  </si>
+  <si>
+    <t>TE-130</t>
+  </si>
+  <si>
+    <t>TE-131</t>
+  </si>
+  <si>
+    <t>TE-132</t>
+  </si>
+  <si>
+    <t>TE-133</t>
+  </si>
+  <si>
+    <t>TE-135</t>
+  </si>
+  <si>
+    <t>TE-136</t>
   </si>
 </sst>
 </file>
@@ -995,6 +995,138 @@
     <xf numFmtId="4" fontId="7" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="distributed"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="distributed"/>
     </xf>
@@ -1030,138 +1162,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1771,167 +1771,167 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="24.75" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="83" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="85"/>
-      <c r="N1" s="92" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="91" t="s">
         <v>32</v>
       </c>
-      <c r="O1" s="93"/>
+      <c r="O1" s="92"/>
     </row>
     <row r="2" spans="1:20" ht="28.5" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="87"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="94"/>
-      <c r="O2" s="95"/>
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="93"/>
+      <c r="O2" s="94"/>
     </row>
     <row r="3" spans="1:20" ht="43.5" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="91"/>
-      <c r="N3" s="94"/>
-      <c r="O3" s="95"/>
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="90"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="94"/>
     </row>
     <row r="4" spans="1:20" ht="35.25" customHeight="1">
-      <c r="A4" s="96" t="s">
+      <c r="A4" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="97"/>
-      <c r="C4" s="98" t="s">
+      <c r="B4" s="54"/>
+      <c r="C4" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="99"/>
-      <c r="M4" s="99"/>
-      <c r="N4" s="99"/>
-      <c r="O4" s="100"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="56"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="57"/>
     </row>
     <row r="5" spans="1:20" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A5" s="101" t="s">
+      <c r="A5" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="77" t="s">
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
-      <c r="K5" s="78"/>
-      <c r="L5" s="79"/>
-      <c r="M5" s="80" t="s">
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="78"/>
+      <c r="M5" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="81"/>
-      <c r="O5" s="82"/>
+      <c r="N5" s="80"/>
+      <c r="O5" s="81"/>
     </row>
     <row r="6" spans="1:20" ht="28.5" customHeight="1">
-      <c r="A6" s="75" t="s">
+      <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="103" t="s">
+      <c r="C6" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="104"/>
-      <c r="E6" s="75" t="s">
+      <c r="D6" s="61"/>
+      <c r="E6" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="75" t="s">
+      <c r="F6" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="75" t="s">
+      <c r="G6" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="75" t="s">
+      <c r="H6" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="75" t="s">
+      <c r="I6" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="75" t="s">
+      <c r="J6" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="75" t="s">
+      <c r="K6" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="75" t="s">
+      <c r="L6" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="M6" s="75" t="s">
+      <c r="M6" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="N6" s="75" t="s">
+      <c r="N6" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="O6" s="75" t="s">
+      <c r="O6" s="51" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="36.75" customHeight="1" thickBot="1">
-      <c r="A7" s="76"/>
-      <c r="B7" s="76"/>
-      <c r="C7" s="105"/>
-      <c r="D7" s="106"/>
-      <c r="E7" s="76"/>
-      <c r="F7" s="76"/>
-      <c r="G7" s="76"/>
-      <c r="H7" s="76"/>
-      <c r="I7" s="76"/>
-      <c r="J7" s="76"/>
-      <c r="K7" s="76"/>
-      <c r="L7" s="76"/>
-      <c r="M7" s="76"/>
-      <c r="N7" s="76"/>
-      <c r="O7" s="76"/>
+      <c r="A7" s="52"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="52"/>
+      <c r="M7" s="52"/>
+      <c r="N7" s="52"/>
+      <c r="O7" s="52"/>
       <c r="Q7" s="5" t="s">
         <v>27</v>
       </c>
@@ -1950,12 +1950,12 @@
         <v>1</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="52"/>
+      <c r="D8" s="96"/>
       <c r="E8" s="24" t="s">
         <v>17</v>
       </c>
@@ -2014,12 +2014,12 @@
         <v>2</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="52"/>
+      <c r="D9" s="96"/>
       <c r="E9" s="24" t="s">
         <v>17</v>
       </c>
@@ -2062,12 +2062,12 @@
         <v>3</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="52"/>
+      <c r="D10" s="96"/>
       <c r="E10" s="24" t="s">
         <v>17</v>
       </c>
@@ -2110,12 +2110,12 @@
         <v>4</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="52"/>
+      <c r="D11" s="96"/>
       <c r="E11" s="24" t="s">
         <v>17</v>
       </c>
@@ -2170,12 +2170,12 @@
         <v>5</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="52"/>
+      <c r="D12" s="96"/>
       <c r="E12" s="24" t="s">
         <v>17</v>
       </c>
@@ -2236,10 +2236,10 @@
       <c r="B13" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="55" t="s">
+      <c r="C13" s="99" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="56"/>
+      <c r="D13" s="100"/>
       <c r="E13" s="30" t="s">
         <v>17</v>
       </c>
@@ -2284,12 +2284,12 @@
       <c r="B14" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="55" t="s">
+      <c r="C14" s="99" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="56"/>
+      <c r="D14" s="100"/>
       <c r="E14" s="30" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F14" s="31">
         <v>46052</v>
@@ -2332,12 +2332,12 @@
       <c r="B15" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="55" t="s">
+      <c r="C15" s="99" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="56"/>
+      <c r="D15" s="100"/>
       <c r="E15" s="30" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F15" s="31">
         <v>46052</v>
@@ -2380,12 +2380,12 @@
       <c r="B16" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="55" t="s">
+      <c r="C16" s="99" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="56"/>
+      <c r="D16" s="100"/>
       <c r="E16" s="30" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F16" s="31">
         <v>46052</v>
@@ -2438,8 +2438,8 @@
         <v>10</v>
       </c>
       <c r="B17" s="24"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="52"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="96"/>
       <c r="E17" s="24"/>
       <c r="F17" s="25"/>
       <c r="G17" s="38"/>
@@ -2473,8 +2473,8 @@
         <v>11</v>
       </c>
       <c r="B18" s="24"/>
-      <c r="C18" s="51"/>
-      <c r="D18" s="52"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="96"/>
       <c r="E18" s="24"/>
       <c r="F18" s="25"/>
       <c r="G18" s="38"/>
@@ -2490,8 +2490,8 @@
     <row r="19" spans="1:20" ht="39.75" customHeight="1">
       <c r="A19" s="23"/>
       <c r="B19" s="24"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="52"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="96"/>
       <c r="E19" s="24"/>
       <c r="F19" s="25"/>
       <c r="G19" s="38"/>
@@ -2507,8 +2507,8 @@
     <row r="20" spans="1:20" ht="39.75" customHeight="1">
       <c r="A20" s="23"/>
       <c r="B20" s="24"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="52"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="96"/>
       <c r="E20" s="24"/>
       <c r="F20" s="25"/>
       <c r="G20" s="38"/>
@@ -2524,8 +2524,8 @@
     <row r="21" spans="1:20" ht="39.75" customHeight="1">
       <c r="A21" s="23"/>
       <c r="B21" s="24"/>
-      <c r="C21" s="51"/>
-      <c r="D21" s="52"/>
+      <c r="C21" s="95"/>
+      <c r="D21" s="96"/>
       <c r="E21" s="24"/>
       <c r="F21" s="25"/>
       <c r="G21" s="38"/>
@@ -2541,8 +2541,8 @@
     <row r="22" spans="1:20" ht="39.75" customHeight="1">
       <c r="A22" s="3"/>
       <c r="B22" s="4"/>
-      <c r="C22" s="53"/>
-      <c r="D22" s="54"/>
+      <c r="C22" s="97"/>
+      <c r="D22" s="98"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
@@ -2558,8 +2558,8 @@
     <row r="23" spans="1:20" ht="39.75" customHeight="1" thickBot="1">
       <c r="A23" s="3"/>
       <c r="B23" s="4"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="54"/>
+      <c r="C23" s="97"/>
+      <c r="D23" s="98"/>
       <c r="E23" s="21"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
@@ -2573,61 +2573,61 @@
       <c r="O23" s="47"/>
     </row>
     <row r="24" spans="1:20" ht="39.75" customHeight="1">
-      <c r="A24" s="67" t="s">
+      <c r="A24" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="68"/>
-      <c r="C24" s="68"/>
-      <c r="D24" s="68"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="68"/>
-      <c r="G24" s="68"/>
-      <c r="H24" s="68"/>
-      <c r="I24" s="68"/>
-      <c r="J24" s="68"/>
-      <c r="K24" s="68"/>
-      <c r="L24" s="68"/>
-      <c r="M24" s="69"/>
-      <c r="N24" s="69"/>
-      <c r="O24" s="70"/>
+      <c r="B24" s="69"/>
+      <c r="C24" s="69"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="69"/>
+      <c r="I24" s="69"/>
+      <c r="J24" s="69"/>
+      <c r="K24" s="69"/>
+      <c r="L24" s="69"/>
+      <c r="M24" s="70"/>
+      <c r="N24" s="70"/>
+      <c r="O24" s="71"/>
     </row>
     <row r="25" spans="1:20" ht="30" customHeight="1" thickBot="1">
-      <c r="A25" s="71"/>
-      <c r="B25" s="72"/>
-      <c r="C25" s="72"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="72"/>
-      <c r="F25" s="72"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="72"/>
-      <c r="I25" s="72"/>
-      <c r="J25" s="72"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="72"/>
-      <c r="M25" s="73"/>
-      <c r="N25" s="73"/>
-      <c r="O25" s="74"/>
+      <c r="A25" s="72"/>
+      <c r="B25" s="73"/>
+      <c r="C25" s="73"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73"/>
+      <c r="J25" s="73"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="73"/>
+      <c r="M25" s="74"/>
+      <c r="N25" s="74"/>
+      <c r="O25" s="75"/>
     </row>
     <row r="26" spans="1:20" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A26" s="60" t="s">
+      <c r="A26" s="104" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="61"/>
-      <c r="C26" s="61"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="61"/>
-      <c r="F26" s="61"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="61"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="57" t="s">
+      <c r="B26" s="105"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="105"/>
+      <c r="E26" s="105"/>
+      <c r="F26" s="105"/>
+      <c r="G26" s="105"/>
+      <c r="H26" s="105"/>
+      <c r="I26" s="106"/>
+      <c r="J26" s="101" t="s">
         <v>3</v>
       </c>
-      <c r="K26" s="58"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="59"/>
+      <c r="K26" s="102"/>
+      <c r="L26" s="102"/>
+      <c r="M26" s="102"/>
+      <c r="N26" s="102"/>
+      <c r="O26" s="103"/>
       <c r="P26" s="14"/>
       <c r="Q26" s="14"/>
     </row>
@@ -2729,16 +2729,21 @@
     <filterColumn colId="12" showButton="0"/>
   </autoFilter>
   <mergeCells count="41">
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:O4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="J26:O26"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A26:I26"/>
     <mergeCell ref="A1:C3"/>
     <mergeCell ref="A24:O25"/>
     <mergeCell ref="A6:A7"/>
@@ -2755,21 +2760,16 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="J26:O26"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:O4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="C6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="M6:M7"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
